--- a/employee_surveys/031_employee_empowerment_evaluation_survey--employee_surveys.xlsx
+++ b/employee_surveys/031_employee_empowerment_evaluation_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>employee_empowerment_evaluation_survey</t>
+          <t>empowerment_frequency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Employee Empowerment Evaluation</t>
+          <t>How often do you feel empowered to make decisions?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>workplace_challenges</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What are your biggest challenges in the workplace?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>job_satisfaction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How would you rate your overall job satisfaction?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>favorite_tools</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Form</t>
+          <t>What are your favorite tools and resources in the workplace?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>autonomy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assigned</t>
+          <t>Do you have the necessary autonomy to make decisions?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>improvement_suggestions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>What are your biggest suggestions for improvement?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>How would you rate your communication with your manager?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>felt_valued</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Do you feel valued and heard in the workplace?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>work_life_balance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How would you rate your work-life balance?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,21 +722,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>role_support</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Do you feel supported in your role?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>areas_for_improvement</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What are some areas where you would like to see more support?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>overall_satisfaction</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>How would you rate your overall satisfaction with the survey?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,136 +827,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>empowerment_frequency_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>empowerment_frequency_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>empowerment_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>empowerment_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>output_file_choices</t>
+          <t>favorite_tools_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>output_file_choices</t>
+          <t>favorite_tools_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>autonomy_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>autonomy_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>felt_valued_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>felt_valued_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>role_support_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>role_support_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
